--- a/claims_log.xlsx
+++ b/claims_log.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -670,7 +670,7 @@
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 14:39:35</t>
+          <t>2026-07-08 19:41:41</t>
         </is>
       </c>
     </row>
@@ -865,6 +865,319 @@
       <c r="U4" s="2" t="inlineStr">
         <is>
           <t>2026-07-08 15:26:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>POL-2024-77650</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Priya Nair</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>01-Apr-2024 to 31-Mar-2025</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28-Jun-2026</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Koramangala, Bengaluru</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Policyholder slipped on a wet floor at a retail store and sustained a fractured wrist.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Priya Nair</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Retail Store Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>priya.nair@email.com, +91-9123456780</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>60000</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Injury</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>medical_report.pdf</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>60000</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>Specialist Queue</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>Routed to Specialist Queue because the claim type is 'injury'.</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 05:36:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>POL-2024-98213</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Anita Sharma</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>01-Mar-2024 to 28-Feb-2025</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>02-Jul-2026</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Whitefield, Bengaluru</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Water damage to kitchen due to burst pipe.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Anita Sharma</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>anita.sharma@email.com</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Property Damage</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>time, asset_id</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>Manual Review</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>Routed to Manual Review because 2 mandatory field(s) are missing: time, asset_id.</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 05:35:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>POL-2024-55011</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Vikram Singh</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>01-Jan-2024 to 31-Dec-2024</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>20-Jun-2026</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Outer Ring Road, Bengaluru</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Vehicle found burned in an isolated area. Witness statements appear inconsistent and the scene looks staged.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Vikram Singh</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Unknown witness</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>vikram.singh@email.com, +91-9988776655</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>KA-01-AB-1234</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>380000</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Vehicle Damage</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>incident_photos.zip</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>380000</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>Investigation Flag</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>Routed to Investigation Flag because the incident description contains flagged keyword(s): inconsistent, staged.</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 12:06:17</t>
         </is>
       </c>
     </row>
